--- a/office/data/工作通讯录.xlsx
+++ b/office/data/工作通讯录.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\glpla.github.io\office\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87424209-3EC1-453E-A02B-3C4E8F1CB336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C87BFB-5C49-40D1-BF99-C9159FB2B87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="普通信笺" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="68">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,22 +59,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>美的全球创新中心**部门</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>华帝公司**部门</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>格力公司**部门</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>海尔公司**部门</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>csv.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -292,6 +276,22 @@
   </si>
   <si>
     <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>美的全球创新中心研发部</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>华帝公司人力资源部</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格力公司创新研究部</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海尔公司策划部</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -665,13 +665,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="22.77734375" customWidth="1"/>
+    <col min="2" max="2" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -682,51 +682,66 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -738,313 +753,313 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E2">
         <v>65</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H2" s="1">
         <v>31048</v>
       </c>
       <c r="I2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E3">
         <v>60</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H3" s="1">
         <v>29254</v>
       </c>
       <c r="I3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E4">
         <v>55</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H4" s="1">
         <v>32183</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E5">
         <v>90</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H5" s="1">
         <v>33107</v>
       </c>
       <c r="I5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E6">
         <v>76</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H6" s="1">
         <v>33859</v>
       </c>
       <c r="I6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>70</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H7" s="1">
         <v>32051</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E8">
         <v>74</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H8" s="1">
         <v>34823</v>
       </c>
       <c r="I8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E9">
         <v>85</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H9" s="1">
         <v>34121</v>
       </c>
       <c r="I9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E10">
         <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H10" s="1">
         <v>35278</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -1053,7 +1068,7 @@
         <v>34881</v>
       </c>
       <c r="I11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
